--- a/develop/ValueSet-mii-vs-diagnose-diagnosecodes-snomed.xlsx
+++ b/develop/ValueSet-mii-vs-diagnose-diagnosecodes-snomed.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-12</t>
+    <t>2026-06-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Purpose</t>
+  </si>
+  <si>
+    <t>Define SNOMED CT concepts allowed for representing diagnoses.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -369,22 +372,24 @@
       <c r="A13" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -406,7 +411,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -414,29 +419,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -458,7 +463,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -466,29 +471,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -510,7 +515,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>1</v>
@@ -518,29 +523,29 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
